--- a/survey_templates/049_workplace_belonging_assessment_survey--survey_templates.xlsx
+++ b/survey_templates/049_workplace_belonging_assessment_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>team_survey</t>
+          <t>team_survey_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Connection</t>
+          <t>Connection (2)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inclusion</t>
+          <t>Inclusion (2)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Job Satisfaction2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Work Satisfaction</t>
+          <t>Work Satisfaction2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Team Leadership</t>
+          <t>Team Leadership2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Feedback2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Additional Comments2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Team Survey3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Connection</t>
+          <t>Connection2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inclusion</t>
+          <t>Inclusion2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Job Satisfaction3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Work Satisfaction</t>
+          <t>Work Satisfaction3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>team_survey_choices</t>
+          <t>team_survey_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>team_survey_choices</t>
+          <t>team_survey_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
